--- a/public/formsExcelTemplates/Tratamiento médico.xlsx
+++ b/public/formsExcelTemplates/Tratamiento médico.xlsx
@@ -16,33 +16,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Sección</t>
-  </si>
-  <si>
-    <t>Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dato requerido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motivo de hospitalización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razón para la hospitalización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolución diaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha y hora</t>
+    <t xml:space="preserve">Fecha y Hora</t>
   </si>
   <si>
     <t xml:space="preserve">Descripción del estado del paciente</t>
   </si>
   <si>
-    <t xml:space="preserve">Tratamiento médico del paciente</t>
+    <t xml:space="preserve">Tratamiento médico</t>
   </si>
 </sst>
 </file>
@@ -79,7 +61,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -88,230 +70,39 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
+      <left style="thin">
+        <color theme="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
+      <top style="thin">
+        <color theme="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,50 +641,79 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="6"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="9"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="12"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" ht="15">
-      <c r="A5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:C5"/>
-  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
